--- a/image source/สมุดรายงานประจำตัวเด็กปฐมวัย_ปริม.xlsx
+++ b/image source/สมุดรายงานประจำตัวเด็กปฐมวัย_ปริม.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shifuu\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shifuu\Desktop\Project\kinder-track\image source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6348070-1B50-4037-A046-AD0ECBD5E788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27704A5E-849C-46E7-B604-2419B3164EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ข้อมูลนักเรียน" sheetId="1" r:id="rId1"/>
@@ -655,33 +655,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1009,7 +1009,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="24"/>
@@ -1018,7 +1018,7 @@
       <c r="E1" s="24"/>
     </row>
     <row r="2" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="24"/>
@@ -1429,32 +1429,32 @@
       <c r="I1" s="24"/>
     </row>
     <row r="2" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="28" t="s">
         <v>49</v>
       </c>
       <c r="E2" s="24"/>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="28" t="s">
         <v>50</v>
       </c>
       <c r="G2" s="24"/>
-      <c r="H2" s="27" t="s">
+      <c r="H2" s="28" t="s">
         <v>55</v>
       </c>
       <c r="I2" s="24"/>
     </row>
     <row r="3" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="27"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
       <c r="D3" s="11" t="s">
         <v>56</v>
       </c>
@@ -1475,7 +1475,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="25" t="s">
         <v>58</v>
       </c>
       <c r="B4" s="24"/>
@@ -1591,7 +1591,7 @@
       <c r="I9" s="12"/>
     </row>
     <row r="10" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="30" t="s">
         <v>65</v>
       </c>
       <c r="B10" s="24"/>
@@ -1751,7 +1751,7 @@
       <c r="I17" s="15"/>
     </row>
     <row r="18" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="27" t="s">
         <v>76</v>
       </c>
       <c r="B18" s="24"/>
@@ -1890,7 +1890,7 @@
       <c r="I24" s="15"/>
     </row>
     <row r="25" spans="1:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="29" t="s">
         <v>87</v>
       </c>
       <c r="B25" s="24"/>
@@ -2071,7 +2071,7 @@
       <c r="I33" s="15"/>
     </row>
     <row r="35" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="23" t="s">
         <v>99</v>
       </c>
       <c r="B35" s="24"/>
@@ -2431,6 +2431,9 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="C19:F21"/>
@@ -2440,9 +2443,6 @@
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="C15:F17"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A23:F23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="99" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
